--- a/data/xlsx/pksf--mobile-phone-servicing.xlsx
+++ b/data/xlsx/pksf--mobile-phone-servicing.xlsx
@@ -648,7 +648,9 @@
       <c r="C16" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -670,7 +672,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -692,7 +696,9 @@
       <c r="C18" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -714,7 +720,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -736,7 +744,9 @@
       <c r="C20" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>9</v>
       </c>
@@ -758,7 +768,9 @@
       <c r="C21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -780,7 +792,9 @@
       <c r="C22" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>8</v>
       </c>
@@ -802,7 +816,9 @@
       <c r="C23" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -824,7 +840,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -846,7 +864,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -868,7 +888,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>6</v>
       </c>
@@ -890,7 +912,9 @@
       <c r="C27" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -912,7 +936,9 @@
       <c r="C28" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>3</v>
       </c>
@@ -934,7 +960,9 @@
       <c r="C29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -956,7 +984,9 @@
       <c r="C30" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>3</v>
       </c>
@@ -978,7 +1008,9 @@
       <c r="C31" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>3</v>
       </c>
@@ -1000,7 +1032,9 @@
       <c r="C32" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>5</v>
       </c>
@@ -1022,7 +1056,9 @@
       <c r="C33" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>7</v>
       </c>
@@ -1044,7 +1080,9 @@
       <c r="C34" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>7</v>
       </c>

--- a/data/xlsx/pksf--mobile-phone-servicing.xlsx
+++ b/data/xlsx/pksf--mobile-phone-servicing.xlsx
@@ -99,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -132,6 +132,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -637,7 +643,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -661,7 +667,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -685,7 +691,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -700,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -709,7 +715,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -733,7 +739,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -757,7 +763,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -781,7 +787,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -796,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -805,7 +811,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -820,7 +826,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -829,7 +835,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -844,7 +850,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -853,7 +859,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -877,7 +883,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -892,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -901,7 +907,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -925,7 +931,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -949,7 +955,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -964,7 +970,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" s="9">
         <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
@@ -973,7 +979,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -997,7 +1003,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1021,7 +1027,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1036,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
@@ -1045,7 +1051,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1060,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F33" s="9">
         <f>IFERROR(MIN(C33,D33)*E33/C33,0)</f>
@@ -1069,7 +1075,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -1084,7 +1090,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F34" s="9">
         <f>IFERROR(MIN(C34,D34)*E34/C34,0)</f>
@@ -1093,7 +1099,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1101,18 +1107,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="10">
+      <c r="E35" s="15">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1121,7 +1127,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="10">
+      <c r="F36" s="15">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -1129,7 +1135,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1138,11 +1144,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="10">
+      <c r="F38" s="15">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="G38" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
